--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104543_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104543_W10.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8851</v>
+        <v>6.0297</v>
       </c>
       <c r="E2" t="n">
-        <v>2.66</v>
+        <v>3.1103</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2251</v>
+        <v>2.9194</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8427</v>
+        <v>2.846</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1124</v>
+        <v>2.1192</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.7268</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4816</v>
+        <v>2.4557</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3031</v>
+        <v>2.2925</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1785</v>
+        <v>0.1632</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3611</v>
+        <v>0.3903</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1908</v>
+        <v>-0.1733</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P2" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0275</v>
+        <v>0.1546</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1785</v>
+        <v>0.6546</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1509</v>
+        <v>-0.5</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5557</v>
+        <v>4.3067</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0334</v>
+        <v>3.3437</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5223</v>
+        <v>0.963</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7847</v>
+        <v>2.762</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5138</v>
+        <v>0.5059</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2709</v>
+        <v>2.2561</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1464</v>
+        <v>3.1036</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9555</v>
+        <v>0.9373</v>
       </c>
       <c r="L3" t="n">
-        <v>2.1909</v>
+        <v>2.1663</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3617</v>
+        <v>-0.3416</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3439</v>
+        <v>1.109</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4748</v>
+        <v>0.8335</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.131</v>
+        <v>0.2755</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1792</v>
+        <v>2.2144</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1712</v>
+        <v>1.4095</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0079</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.438</v>
+        <v>-0.4301</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9712</v>
+        <v>-0.9681</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5331</v>
+        <v>0.538</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0254</v>
+        <v>-0.0304</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L4" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4126</v>
+        <v>-0.3997</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2368</v>
+        <v>-0.2301</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>1.844</v>
+        <v>0.8721</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1039</v>
+        <v>0.3505</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7401</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. UDEZE</t>
+          <t>S. EVANS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8687</v>
+        <v>1.6141</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3136</v>
+        <v>2.1358</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1823</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9117</v>
+        <v>2.0679</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.1703</v>
+        <v>1.549</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2586</v>
+        <v>0.5189</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.0464</v>
+        <v>3.1683</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.3822</v>
+        <v>2.2538</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3359</v>
+        <v>0.9145</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8653</v>
+        <v>-1.1004</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.788</v>
+        <v>-0.7048</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0772</v>
+        <v>-0.3956</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>3.4145</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4609</v>
+        <v>0.0046</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9084</v>
+        <v>0.6614</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5524</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>-0.4584</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.7205</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7531</v>
+        <v>1.3641</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2842</v>
+        <v>0.1692</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0373</v>
+        <v>1.1949</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6216</v>
+        <v>0.6298</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.8609</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2266</v>
+        <v>-0.2311</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7592</v>
+        <v>0.7409</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6927</v>
+        <v>0.6895</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0665</v>
+        <v>0.0515</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1375</v>
+        <v>-0.1111</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1556</v>
+        <v>0.1715</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3883</v>
+        <v>0.2091</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0907</v>
+        <v>0.5664</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4791</v>
+        <v>-0.3573</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. EVANS</t>
+          <t>M. UDEZE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5785</v>
+        <v>1.3404</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3375</v>
+        <v>-1.1525</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.759</v>
+        <v>2.4929</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1068</v>
+        <v>-1.8988</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5659</v>
+        <v>-2.1658</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5409</v>
+        <v>0.267</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2433</v>
+        <v>-1.0545</v>
       </c>
       <c r="K7" t="n">
-        <v>2.292</v>
+        <v>-1.3897</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9513</v>
+        <v>0.3351</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1365</v>
+        <v>-0.8442</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7261</v>
+        <v>-0.7761</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4104</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>3.4025</v>
+        <v>2.5039</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0785</v>
+        <v>1.9221</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2389</v>
+        <v>1.0889</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8396</v>
+        <v>0.8331</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.4498</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7355</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1615</v>
+        <v>0.319</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.5728</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7285</v>
+        <v>0.8919</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2609</v>
+        <v>1.2655</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3333</v>
+        <v>0.3359</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9276</v>
+        <v>0.9296</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7063</v>
+        <v>0.7047</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5546</v>
+        <v>0.5608</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2986</v>
+        <v>0.3014</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1921</v>
+        <v>-0.0359</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0529</v>
+        <v>0.1035</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>R. LUZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0803</v>
+        <v>-0.5599</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4563</v>
+        <v>1.8052</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5366</v>
+        <v>-2.3651</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9734</v>
+        <v>1.1421</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7388</v>
+        <v>-0.1495</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2346</v>
+        <v>1.2917</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4156</v>
+        <v>1.355</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3782</v>
+        <v>0.0517</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>1.3033</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5578</v>
+        <v>-0.2129</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3605</v>
+        <v>-0.2012</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1973</v>
+        <v>-0.0116</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.8562</v>
+        <v>1.5934</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.5367</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0614</v>
+        <v>0.36</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2994</v>
+        <v>0.2925</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3608</v>
+        <v>0.0675</v>
       </c>
       <c r="V9" t="n">
-        <v>1.8639</v>
+        <v>-3.6554</v>
       </c>
       <c r="W9" t="n">
-        <v>3.278</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4141</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. LUZ</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.7148</v>
       </c>
       <c r="E10" t="n">
-        <v>2.045</v>
+        <v>0.0156</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5798</v>
+        <v>-0.7304</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1345</v>
+        <v>1.9777</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.153</v>
+        <v>1.7377</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2875</v>
+        <v>0.2401</v>
       </c>
       <c r="J10" t="n">
-        <v>1.358</v>
+        <v>1.4022</v>
       </c>
       <c r="K10" t="n">
-        <v>0.052</v>
+        <v>1.365</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3061</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2236</v>
+        <v>0.5755</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.205</v>
+        <v>0.3727</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0186</v>
+        <v>0.2028</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5878</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-4.5526</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4065</v>
+        <v>-0.6862</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5263</v>
+        <v>-0.1024</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1198</v>
+        <v>-0.5838</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.6636</v>
+        <v>1.8634</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>3.2684</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.8243</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3166</v>
+        <v>-1.5191</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1987</v>
+        <v>-1.44</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.118</v>
+        <v>-0.0791</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9862</v>
+        <v>-0.9861</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1999</v>
+        <v>-0.1965</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5108</v>
+        <v>0.3077</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6472</v>
+        <v>0.4133</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0368</v>
+        <v>-1.8224</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9422</v>
+        <v>-1.8945</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0946</v>
+        <v>0.0721</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0433</v>
+        <v>-1.0524</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1125</v>
+        <v>-1.1115</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0692</v>
+        <v>0.0591</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7052</v>
+        <v>-0.7237</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0292</v>
+        <v>0.0142</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3381</v>
+        <v>-0.3287</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.313</v>
+        <v>-0.0871</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1028</v>
+        <v>-0.0327</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2102</v>
+        <v>-0.0545</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0115</v>
+        <v>-4.212</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7306</v>
+        <v>-3.2042</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.281</v>
+        <v>-1.0078</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.7479</v>
+        <v>-1.7382</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2122</v>
+        <v>-1.2066</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5357</v>
+        <v>-0.5316</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.9008</v>
+        <v>-1.9125</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.2264</v>
+        <v>-1.2345</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1529</v>
+        <v>0.1743</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9441</v>
+        <v>-1.1567</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6956</v>
+        <v>-0.1535</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2485</v>
+        <v>-1.0031</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.001799999999999</v>
+        <v>8.360200000000003</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6671</v>
+        <v>3.725300000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>4.3344</v>
+        <v>4.635</v>
       </c>
       <c r="G14" t="n">
-        <v>6.5975</v>
+        <v>6.585400000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7068999999999996</v>
+        <v>0.7175000000000007</v>
       </c>
       <c r="I14" t="n">
-        <v>5.8905</v>
+        <v>5.868099999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>8.720900000000002</v>
+        <v>8.494100000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8443</v>
+        <v>2.734700000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>5.8766</v>
+        <v>5.7597</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1234</v>
+        <v>-1.9087</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.1376</v>
+        <v>-2.0169</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01409999999999992</v>
+        <v>0.1082999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>1.134200000000001</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.0127</v>
+        <v>-17.0726</v>
       </c>
       <c r="R14" t="n">
-        <v>18.1467</v>
+        <v>18.2105</v>
       </c>
       <c r="S14" t="n">
-        <v>2.616200000000001</v>
+        <v>2.973299999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>4.0528</v>
+        <v>4.433099999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.4367</v>
+        <v>-1.4599</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.346000000000001</v>
+        <v>-2.3368</v>
       </c>
       <c r="W14" t="n">
-        <v>7.905900000000001</v>
+        <v>7.8704</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.2519</v>
+        <v>-10.2072</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. BURJANADZE</t>
+          <t>M. THOMAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2466</v>
+        <v>2.9629</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8808</v>
+        <v>1.4351</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6343</v>
+        <v>1.5279</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.11</v>
+        <v>-0.4137</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6146</v>
+        <v>-2.8776</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7246</v>
+        <v>2.464</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0973</v>
+        <v>1.2868</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0173</v>
+        <v>-1.9003</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1147</v>
+        <v>3.187</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0126</v>
+        <v>-1.7004</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5973000000000001</v>
+        <v>-0.9774</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6099</v>
+        <v>-0.723</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.8211</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6805</v>
+        <v>3.4145</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7836</v>
+        <v>-0.5506</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0858</v>
+        <v>-0.2096</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3021</v>
+        <v>-0.341</v>
       </c>
       <c r="V15" t="n">
-        <v>2.8924</v>
+        <v>2.3337</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8924</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.1548</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. THOMAS</t>
+          <t>B. BURJANADZE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3835</v>
+        <v>2.6657</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2456</v>
+        <v>3.16</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1379</v>
+        <v>-0.4943</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.414</v>
+        <v>-1.1018</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.8743</v>
+        <v>0.6201</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4603</v>
+        <v>-1.7219</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3225</v>
+        <v>-0.1021</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.8813</v>
+        <v>0.0172</v>
       </c>
       <c r="L16" t="n">
-        <v>3.2038</v>
+        <v>-0.1194</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7365</v>
+        <v>-0.9997</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.993</v>
+        <v>0.6028</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7435</v>
+        <v>-1.6025</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8147</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.4025</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1299</v>
+        <v>0.2031</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4476</v>
+        <v>0.3807</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6823</v>
+        <v>-0.1775</v>
       </c>
       <c r="V16" t="n">
-        <v>2.3396</v>
+        <v>2.8814</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1853</v>
+        <v>2.8814</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1542</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. BOZIC</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0988</v>
+        <v>1.8486</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8835</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2154</v>
+        <v>1.2492</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0689</v>
+        <v>2.5929</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0737</v>
+        <v>1.9562</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0048</v>
+        <v>0.6368</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1922</v>
+        <v>3.2921</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6108</v>
+        <v>3.1059</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4186</v>
+        <v>0.1862</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1233</v>
+        <v>-0.6992</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5371</v>
+        <v>-1.1497</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5862000000000001</v>
+        <v>0.4506</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.1757</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-6.3513</v>
+        <v>-2.9592</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1757</v>
+        <v>2.7316</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5446</v>
+        <v>-0.2845</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2824</v>
+        <v>0.1087</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2622</v>
+        <v>-0.3932</v>
       </c>
       <c r="V17" t="n">
-        <v>2.661</v>
+        <v>-0.2322</v>
       </c>
       <c r="W17" t="n">
-        <v>3.7602</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0991</v>
+        <v>-0.3899</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>L. BOZIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4088</v>
+        <v>1.2645</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.212</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8951</v>
+        <v>1.0526</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5822</v>
+        <v>1.0623</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9611</v>
+        <v>2.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6212</v>
+        <v>-0.9977</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3138</v>
+        <v>2.1454</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1272</v>
+        <v>2.5781</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1866</v>
+        <v>-0.4326</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7316</v>
+        <v>-1.0831</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1662</v>
+        <v>-0.518</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4346</v>
+        <v>-0.5651</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2268</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9488</v>
+        <v>-6.3737</v>
       </c>
       <c r="R18" t="n">
-        <v>2.722</v>
+        <v>3.1868</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7153</v>
+        <v>0.7398</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0121</v>
+        <v>0.6985</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7032</v>
+        <v>0.0413</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2314</v>
+        <v>2.6493</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>3.7417</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3921</v>
+        <v>-1.0924</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. TOMAS</t>
+          <t>E. DURAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6454</v>
+        <v>-1.3859</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9577</v>
+        <v>-1.7054</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6877</v>
+        <v>0.3195</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3699</v>
+        <v>-1.0764</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0318</v>
+        <v>0.327</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3381</v>
+        <v>-1.4034</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.749</v>
+        <v>-1.4359</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.0689</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.749</v>
+        <v>-1.5048</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6209</v>
+        <v>0.3595</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0318</v>
+        <v>0.2581</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5891</v>
+        <v>0.1014</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5024</v>
+        <v>-0.079</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2087</v>
+        <v>0.1857</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2937</v>
+        <v>-0.2647</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. DURAN</t>
+          <t>P. TOMAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9095</v>
+        <v>-1.6132</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9339</v>
+        <v>-0.9615</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0244</v>
+        <v>-0.6516</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0792</v>
+        <v>-1.3681</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3202</v>
+        <v>-0.0289</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3994</v>
+        <v>-1.3392</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4288</v>
+        <v>-0.7524</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0693</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4981</v>
+        <v>-0.7524</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3496</v>
+        <v>-0.6157</v>
       </c>
       <c r="N20" t="n">
-        <v>0.251</v>
+        <v>-0.0289</v>
       </c>
       <c r="O20" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.5868</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.597</v>
+        <v>-0.4727</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0514</v>
+        <v>-0.2091</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5456</v>
+        <v>-0.2636</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.0065</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.0065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2004</v>
+        <v>-1.8566</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1858</v>
+        <v>-2.9757</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9854000000000001</v>
+        <v>1.1191</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2797</v>
+        <v>-2.2678</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7013</v>
+        <v>-1.6976</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5784</v>
+        <v>-0.5702</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8177</v>
+        <v>-0.8383</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.551</v>
+        <v>-0.5623</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.462</v>
+        <v>-1.4295</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1503</v>
+        <v>-1.1353</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3117</v>
+        <v>-0.2942</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3744</v>
+        <v>-0.0441</v>
       </c>
       <c r="T21" t="n">
-        <v>0.127</v>
+        <v>0.3665</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-0.4107</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9767</v>
+        <v>-2.4889</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.59</v>
+        <v>-1.521</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3868</v>
+        <v>-0.9679</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9273</v>
+        <v>-1.9394</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.997</v>
+        <v>-1.0021</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9303</v>
+        <v>-0.9373</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5448</v>
+        <v>-0.5821</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8698</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.325</v>
+        <v>0.3045</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3825</v>
+        <v>-1.3573</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2554</v>
+        <v>-1.2417</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R22" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1836</v>
+        <v>0.3123</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1966</v>
+        <v>0.3178</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3802</v>
+        <v>-0.0055</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0057</v>
+        <v>-3.7626</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3224</v>
+        <v>-2.3546</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6832</v>
+        <v>-1.408</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2638</v>
+        <v>-1.2704</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.704</v>
+        <v>-0.7118</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5598</v>
+        <v>-0.5586</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6862</v>
+        <v>-0.7144</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4196</v>
+        <v>-0.4384</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5776</v>
+        <v>-0.556</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8961</v>
+        <v>-0.6469</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0484</v>
+        <v>-0.0468</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8478</v>
+        <v>-0.6002</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9384</v>
+        <v>-0.9347</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.9384</v>
+        <v>-0.9347</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4016</v>
+        <v>-4.0671</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8682</v>
+        <v>-0.5231</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5334</v>
+        <v>-3.5441</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8048</v>
+        <v>-0.8033</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6319</v>
+        <v>0.6373</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4368</v>
+        <v>-1.4406</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3813</v>
+        <v>-0.3905</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.4159</v>
+        <v>-0.4249</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4236</v>
+        <v>-0.4129</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6028</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5456</v>
+        <v>-0.223</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4869</v>
+        <v>-0.1326</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0587</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.0016</v>
+        <v>-6.432599999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3345</v>
+        <v>-4.634899999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.6672</v>
+        <v>-1.7976</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.5976</v>
+        <v>-6.585699999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7068999999999993</v>
+        <v>-0.7174000000000009</v>
       </c>
       <c r="I25" t="n">
-        <v>-5.8907</v>
+        <v>-5.8681</v>
       </c>
       <c r="J25" t="n">
-        <v>2.123400000000001</v>
+        <v>1.9086</v>
       </c>
       <c r="K25" t="n">
-        <v>2.1375</v>
+        <v>2.017</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.01409999999999989</v>
+        <v>-0.1084000000000002</v>
       </c>
       <c r="M25" t="n">
-        <v>-8.721</v>
+        <v>-8.494300000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.8444</v>
+        <v>-2.7345</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.8766</v>
+        <v>-5.7596</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q25" t="n">
-        <v>-18.1467</v>
+        <v>-18.2105</v>
       </c>
       <c r="R25" t="n">
-        <v>17.0124</v>
+        <v>17.0723</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.6161</v>
+        <v>-1.0456</v>
       </c>
       <c r="T25" t="n">
-        <v>1.4367</v>
+        <v>1.4598</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.0529</v>
+        <v>-2.5055</v>
       </c>
       <c r="V25" t="n">
-        <v>2.346000000000001</v>
+        <v>2.336599999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>10.252</v>
+        <v>10.207</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.906000000000001</v>
+        <v>-7.8703</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104543_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104543_W10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-10.2072</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.1548</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.3899</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0924</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.003</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.9347</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104543_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-7.8703</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
